--- a/dorixonalar.xlsx
+++ b/dorixonalar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ikromov Nodir\Desktop\dorixona_bot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\gpp\dorixona-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41AB2F0C-D132-44F0-A12A-9EB9A8EAFA44}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CA63C2-EC80-49BC-BDA8-A3E92373DCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="482">
   <si>
     <t>Filial №</t>
   </si>
@@ -1358,6 +1358,114 @@
   </si>
   <si>
     <t>асосий</t>
+  </si>
+  <si>
+    <t>41.221647</t>
+  </si>
+  <si>
+    <t>69.209133</t>
+  </si>
+  <si>
+    <t>41.255195</t>
+  </si>
+  <si>
+    <t>69.343233</t>
+  </si>
+  <si>
+    <t>41.364346</t>
+  </si>
+  <si>
+    <t>69.212662</t>
+  </si>
+  <si>
+    <t>39.655814</t>
+  </si>
+  <si>
+    <t>66.907764</t>
+  </si>
+  <si>
+    <t>41.355202</t>
+  </si>
+  <si>
+    <t>69.387615</t>
+  </si>
+  <si>
+    <t>41.368009</t>
+  </si>
+  <si>
+    <t>69.292278</t>
+  </si>
+  <si>
+    <t>41.372681</t>
+  </si>
+  <si>
+    <t>69.311321</t>
+  </si>
+  <si>
+    <t>69.218738</t>
+  </si>
+  <si>
+    <t>41.322283</t>
+  </si>
+  <si>
+    <t>69.335688</t>
+  </si>
+  <si>
+    <t>41.340859</t>
+  </si>
+  <si>
+    <t>69.347067</t>
+  </si>
+  <si>
+    <t>41.279685</t>
+  </si>
+  <si>
+    <t>69.223747</t>
+  </si>
+  <si>
+    <t>41.282963</t>
+  </si>
+  <si>
+    <t>69.189548</t>
+  </si>
+  <si>
+    <t>41.268135</t>
+  </si>
+  <si>
+    <t>41.367832</t>
+  </si>
+  <si>
+    <t>69.313211</t>
+  </si>
+  <si>
+    <t>69.449985</t>
+  </si>
+  <si>
+    <t>41.403362</t>
+  </si>
+  <si>
+    <t>69.210383</t>
+  </si>
+  <si>
+    <t>41.219362</t>
+  </si>
+  <si>
+    <t>41.334940</t>
+  </si>
+  <si>
+    <t>69.370458</t>
+  </si>
+  <si>
+    <t>41.322426</t>
+  </si>
+  <si>
+    <t>69.218730</t>
+  </si>
+  <si>
+    <t>69.212527</t>
+  </si>
+  <si>
+    <t>41.198960</t>
   </si>
 </sst>
 </file>
@@ -1698,12 +1806,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P102"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.109375" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1753,7 +1861,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>445</v>
       </c>
@@ -1797,7 +1905,7 @@
         <v>69.252401000000006</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1841,7 +1949,7 @@
         <v>69.174616</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1885,7 +1993,7 @@
         <v>69.358986000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1929,7 +2037,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1973,7 +2081,7 @@
         <v>69.385855000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2017,7 +2125,7 @@
         <v>69.348903800000002</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2061,7 +2169,7 @@
         <v>69.266099999999994</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2105,7 +2213,7 @@
         <v>69.285818000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2142,14 +2250,14 @@
       <c r="N10" t="s">
         <v>58</v>
       </c>
-      <c r="O10">
-        <v>41.248617000000003</v>
-      </c>
-      <c r="P10">
-        <v>69.329485000000005</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O10" t="s">
+        <v>448</v>
+      </c>
+      <c r="P10" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2193,7 +2301,7 @@
         <v>69.301205999999993</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2237,7 +2345,7 @@
         <v>69.359245999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2274,14 +2382,14 @@
       <c r="N13" t="s">
         <v>70</v>
       </c>
-      <c r="O13">
-        <v>41.372663000000003</v>
-      </c>
-      <c r="P13">
-        <v>69.311321000000007</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O13" t="s">
+        <v>458</v>
+      </c>
+      <c r="P13" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2325,7 +2433,7 @@
         <v>69.289861000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2369,7 +2477,7 @@
         <v>69.256793999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2413,7 +2521,7 @@
         <v>69.174408999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2457,7 +2565,7 @@
         <v>69.213961999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2501,7 +2609,7 @@
         <v>69.303685999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2538,14 +2646,14 @@
       <c r="N19" t="s">
         <v>93</v>
       </c>
-      <c r="O19">
-        <v>41.321019</v>
-      </c>
-      <c r="P19">
-        <v>69.214618000000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O19" t="s">
+        <v>478</v>
+      </c>
+      <c r="P19" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2589,7 +2697,7 @@
         <v>69.167536999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2633,7 +2741,7 @@
         <v>69.208455000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2670,14 +2778,14 @@
       <c r="N22" t="s">
         <v>106</v>
       </c>
-      <c r="O22">
-        <v>41.268349999999998</v>
-      </c>
-      <c r="P22">
-        <v>69.363827999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O22" t="s">
+        <v>454</v>
+      </c>
+      <c r="P22" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2714,14 +2822,14 @@
       <c r="N23" t="s">
         <v>111</v>
       </c>
-      <c r="O23">
-        <v>41.262594300000003</v>
-      </c>
-      <c r="P23">
-        <v>69.154735799999997</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O23" t="s">
+        <v>467</v>
+      </c>
+      <c r="P23" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2765,7 +2873,7 @@
         <v>69.216064000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2809,7 +2917,7 @@
         <v>69.357530999999994</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2853,7 +2961,7 @@
         <v>69.245779999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2897,7 +3005,7 @@
         <v>69.163979999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2941,7 +3049,7 @@
         <v>69.240731999999994</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2978,14 +3086,14 @@
       <c r="N29" t="s">
         <v>134</v>
       </c>
-      <c r="O29">
-        <v>41.321019</v>
-      </c>
-      <c r="P29">
-        <v>69.214618000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O29" t="s">
+        <v>461</v>
+      </c>
+      <c r="P29" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3023,7 +3131,7 @@
         <v>69.370960999999994</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3067,7 +3175,7 @@
         <v>69.348903800000002</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3104,14 +3212,14 @@
       <c r="N32" t="s">
         <v>146</v>
       </c>
-      <c r="O32">
-        <v>41.364677999999998</v>
+      <c r="O32" t="s">
+        <v>450</v>
       </c>
       <c r="P32">
         <v>69.212119999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3151,11 +3259,11 @@
       <c r="O33">
         <v>41.288673000000003</v>
       </c>
-      <c r="P33">
-        <v>69.316046</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P33" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3199,7 +3307,7 @@
         <v>69.295582999999993</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3243,7 +3351,7 @@
         <v>69.307854000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3287,7 +3395,7 @@
         <v>67.274966000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3331,7 +3439,7 @@
         <v>69.250658000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3368,14 +3476,14 @@
       <c r="N38" t="s">
         <v>172</v>
       </c>
-      <c r="O38">
-        <v>39.898266</v>
-      </c>
-      <c r="P38">
-        <v>66.253645000000006</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O38" t="s">
+        <v>452</v>
+      </c>
+      <c r="P38" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3419,7 +3527,7 @@
         <v>69.359793999999994</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3463,7 +3571,7 @@
         <v>67.089285000000004</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3507,7 +3615,7 @@
         <v>69.193569999999994</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>40</v>
       </c>
@@ -3544,14 +3652,14 @@
       <c r="N42" t="s">
         <v>188</v>
       </c>
-      <c r="O42">
-        <v>41.291113000000003</v>
-      </c>
-      <c r="P42">
-        <v>69.343166999999994</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O42" t="s">
+        <v>465</v>
+      </c>
+      <c r="P42" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -3595,7 +3703,7 @@
         <v>69.316505000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>42</v>
       </c>
@@ -3632,14 +3740,14 @@
       <c r="N44" t="s">
         <v>196</v>
       </c>
-      <c r="O44">
-        <v>41.270566000000002</v>
-      </c>
-      <c r="P44">
-        <v>69.182754000000003</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O44" t="s">
+        <v>469</v>
+      </c>
+      <c r="P44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -3683,7 +3791,7 @@
         <v>69.173951000000002</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>44</v>
       </c>
@@ -3720,14 +3828,14 @@
       <c r="N46" t="s">
         <v>204</v>
       </c>
-      <c r="O46">
-        <v>41.199567999999999</v>
-      </c>
-      <c r="P46">
-        <v>69.227742000000006</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O46" t="s">
+        <v>456</v>
+      </c>
+      <c r="P46" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>45</v>
       </c>
@@ -3771,7 +3879,7 @@
         <v>69.196364000000003</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>46</v>
       </c>
@@ -3808,14 +3916,14 @@
       <c r="N48" t="s">
         <v>212</v>
       </c>
-      <c r="O48">
-        <v>41.336857000000002</v>
-      </c>
-      <c r="P48">
-        <v>69.288531000000006</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O48" t="s">
+        <v>470</v>
+      </c>
+      <c r="P48" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>47</v>
       </c>
@@ -3859,7 +3967,7 @@
         <v>69.280490999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>48</v>
       </c>
@@ -3903,7 +4011,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>49</v>
       </c>
@@ -3947,7 +4055,7 @@
         <v>69.165317999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>50</v>
       </c>
@@ -3991,7 +4099,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>51</v>
       </c>
@@ -4035,7 +4143,7 @@
         <v>69.165398999999994</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>52</v>
       </c>
@@ -4072,14 +4180,14 @@
       <c r="N54" t="s">
         <v>237</v>
       </c>
-      <c r="O54">
-        <v>41.403295999999997</v>
-      </c>
-      <c r="P54">
-        <v>69.450066000000007</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O54" t="s">
+        <v>473</v>
+      </c>
+      <c r="P54" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>53</v>
       </c>
@@ -4123,7 +4231,7 @@
         <v>66.927318</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>54</v>
       </c>
@@ -4167,7 +4275,7 @@
         <v>69.293795000000003</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>55</v>
       </c>
@@ -4204,14 +4312,14 @@
       <c r="N57" t="s">
         <v>250</v>
       </c>
-      <c r="O57">
-        <v>41.37265</v>
-      </c>
-      <c r="P57">
-        <v>69.268525999999994</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O57" t="s">
+        <v>475</v>
+      </c>
+      <c r="P57" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>56</v>
       </c>
@@ -4248,14 +4356,14 @@
       <c r="N58" t="s">
         <v>254</v>
       </c>
-      <c r="O58">
-        <v>41.216839999999998</v>
-      </c>
-      <c r="P58">
-        <v>69.216611999999998</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O58" t="s">
+        <v>446</v>
+      </c>
+      <c r="P58" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>57</v>
       </c>
@@ -4299,7 +4407,7 @@
         <v>69.214106000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>58</v>
       </c>
@@ -4336,14 +4444,14 @@
       <c r="N60" t="s">
         <v>262</v>
       </c>
-      <c r="O60">
-        <v>38.911031999999999</v>
-      </c>
-      <c r="P60">
-        <v>72.224108999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O60" t="s">
+        <v>481</v>
+      </c>
+      <c r="P60" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>59</v>
       </c>
@@ -4387,7 +4495,7 @@
         <v>69.223591999999996</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>60</v>
       </c>
@@ -4431,7 +4539,7 @@
         <v>69.354242999999997</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>61</v>
       </c>
@@ -4475,7 +4583,7 @@
         <v>69.165668999999994</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>62</v>
       </c>
@@ -4519,7 +4627,7 @@
         <v>69.276124999999993</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>63</v>
       </c>
@@ -4563,7 +4671,7 @@
         <v>69.186194999999998</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>64</v>
       </c>
@@ -4607,7 +4715,7 @@
         <v>69.181030000000007</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>65</v>
       </c>
@@ -4651,7 +4759,7 @@
         <v>69.346453999999994</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>66</v>
       </c>
@@ -4695,7 +4803,7 @@
         <v>69.216072999999994</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>67</v>
       </c>
@@ -4739,7 +4847,7 @@
         <v>69.259471000000005</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>68</v>
       </c>
@@ -4783,7 +4891,7 @@
         <v>69.370582999999996</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>69</v>
       </c>
@@ -4827,7 +4935,7 @@
         <v>69.338719999999995</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>70</v>
       </c>
@@ -4871,7 +4979,7 @@
         <v>69.339078999999998</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>71</v>
       </c>
@@ -4915,7 +5023,7 @@
         <v>69.368796000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>72</v>
       </c>
@@ -4959,7 +5067,7 @@
         <v>69.073375999999996</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>73</v>
       </c>
@@ -5003,7 +5111,7 @@
         <v>69.364286000000007</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>74</v>
       </c>
@@ -5047,7 +5155,7 @@
         <v>66.892122000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>75</v>
       </c>
@@ -5091,7 +5199,7 @@
         <v>66.918550999999994</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>76</v>
       </c>
@@ -5135,7 +5243,7 @@
         <v>69.335611999999998</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>77</v>
       </c>
@@ -5179,7 +5287,7 @@
         <v>69.154628000000002</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>78</v>
       </c>
@@ -5223,7 +5331,7 @@
         <v>69.280086999999995</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>79</v>
       </c>
@@ -5267,7 +5375,7 @@
         <v>69.178272000000007</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>80</v>
       </c>
@@ -5311,7 +5419,7 @@
         <v>70.094517999999994</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>81</v>
       </c>
@@ -5355,7 +5463,7 @@
         <v>69.289069999999995</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>82</v>
       </c>
@@ -5392,14 +5500,14 @@
       <c r="N84" t="s">
         <v>360</v>
       </c>
-      <c r="O84">
-        <v>41.336551999999998</v>
-      </c>
-      <c r="P84">
-        <v>69.368948000000003</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O84" t="s">
+        <v>476</v>
+      </c>
+      <c r="P84" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>83</v>
       </c>
@@ -5443,7 +5551,7 @@
         <v>69.164356999999995</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>84</v>
       </c>
@@ -5487,7 +5595,7 @@
         <v>66.944485</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>85</v>
       </c>
@@ -5531,7 +5639,7 @@
         <v>69.461366999999996</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>86</v>
       </c>
@@ -5575,7 +5683,7 @@
         <v>69.311249000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>87</v>
       </c>
@@ -5612,14 +5720,14 @@
       <c r="N89" t="s">
         <v>380</v>
       </c>
-      <c r="O89">
-        <v>41.343525</v>
-      </c>
-      <c r="P89">
-        <v>69.336303999999998</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O89" t="s">
+        <v>463</v>
+      </c>
+      <c r="P89" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>88</v>
       </c>
@@ -5663,7 +5771,7 @@
         <v>66.924533999999994</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>89</v>
       </c>
@@ -5707,7 +5815,7 @@
         <v>67.014419000000004</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>90</v>
       </c>
@@ -5751,7 +5859,7 @@
         <v>69.192195999999996</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>91</v>
       </c>
@@ -5795,7 +5903,7 @@
         <v>69.211447000000007</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>92</v>
       </c>
@@ -5839,7 +5947,7 @@
         <v>69.223870000000005</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>93</v>
       </c>
@@ -5883,7 +5991,7 @@
         <v>66.512476000000007</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>94</v>
       </c>
@@ -5927,7 +6035,7 @@
         <v>69.228810999999993</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>95</v>
       </c>
@@ -5971,7 +6079,7 @@
         <v>69.656004999999993</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>96</v>
       </c>
@@ -6015,7 +6123,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>97</v>
       </c>
@@ -6059,7 +6167,7 @@
         <v>59.462820999999998</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>98</v>
       </c>
@@ -6103,7 +6211,7 @@
         <v>69.341612999999995</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>99</v>
       </c>
@@ -6147,7 +6255,7 @@
         <v>69.406992000000002</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>100</v>
       </c>

--- a/dorixonalar.xlsx
+++ b/dorixonalar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\gpp\dorixona-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CA63C2-EC80-49BC-BDA8-A3E92373DCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E982DBC1-6F7B-43FD-899C-E912BF792A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="487">
   <si>
     <t>Filial №</t>
   </si>
@@ -1396,12 +1396,6 @@
     <t>69.292278</t>
   </si>
   <si>
-    <t>41.372681</t>
-  </si>
-  <si>
-    <t>69.311321</t>
-  </si>
-  <si>
     <t>69.218738</t>
   </si>
   <si>
@@ -1466,6 +1460,27 @@
   </si>
   <si>
     <t>41.198960</t>
+  </si>
+  <si>
+    <t>41.374547</t>
+  </si>
+  <si>
+    <t>69.303788</t>
+  </si>
+  <si>
+    <t>41.204318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.216266 </t>
+  </si>
+  <si>
+    <t>69.218276</t>
+  </si>
+  <si>
+    <t>41.322175</t>
+  </si>
+  <si>
+    <t>1-сонли Шахар тугрихонаси рупараси</t>
   </si>
 </sst>
 </file>
@@ -2383,10 +2398,10 @@
         <v>70</v>
       </c>
       <c r="O13" t="s">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="P13" t="s">
-        <v>459</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -2544,7 +2559,7 @@
         <v>84</v>
       </c>
       <c r="J17" t="s">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="K17" t="s">
         <v>85</v>
@@ -2558,11 +2573,11 @@
       <c r="N17" t="s">
         <v>86</v>
       </c>
-      <c r="O17">
-        <v>41.321046000000003</v>
-      </c>
-      <c r="P17">
-        <v>69.213961999999995</v>
+      <c r="O17" t="s">
+        <v>485</v>
+      </c>
+      <c r="P17" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -2647,10 +2662,10 @@
         <v>93</v>
       </c>
       <c r="O19" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P19" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -2823,10 +2838,10 @@
         <v>111</v>
       </c>
       <c r="O23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="P23" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -3087,10 +3102,10 @@
         <v>134</v>
       </c>
       <c r="O29" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="P29" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -3653,10 +3668,10 @@
         <v>188</v>
       </c>
       <c r="O42" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="P42" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -3741,10 +3756,10 @@
         <v>196</v>
       </c>
       <c r="O44" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="P44" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -3917,10 +3932,10 @@
         <v>212</v>
       </c>
       <c r="O48" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="P48" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -4181,10 +4196,10 @@
         <v>237</v>
       </c>
       <c r="O54" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="P54" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
@@ -4313,10 +4328,10 @@
         <v>250</v>
       </c>
       <c r="O57" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="P57" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
@@ -4445,10 +4460,10 @@
         <v>262</v>
       </c>
       <c r="O60" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P60" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
@@ -4796,11 +4811,11 @@
       <c r="N68" t="s">
         <v>295</v>
       </c>
-      <c r="O68">
-        <v>41.204534000000002</v>
-      </c>
-      <c r="P68">
-        <v>69.216072999999994</v>
+      <c r="O68" t="s">
+        <v>482</v>
+      </c>
+      <c r="P68" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
@@ -5501,10 +5516,10 @@
         <v>360</v>
       </c>
       <c r="O84" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="P84" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
@@ -5721,10 +5736,10 @@
         <v>380</v>
       </c>
       <c r="O89" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="P89" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">

--- a/dorixonalar.xlsx
+++ b/dorixonalar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\gpp\dorixona-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E982DBC1-6F7B-43FD-899C-E912BF792A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6E8430-B35C-4302-B419-197A20C09D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="490">
   <si>
     <t>Filial №</t>
   </si>
@@ -1360,18 +1360,9 @@
     <t>асосий</t>
   </si>
   <si>
-    <t>41.221647</t>
-  </si>
-  <si>
-    <t>69.209133</t>
-  </si>
-  <si>
     <t>41.255195</t>
   </si>
   <si>
-    <t>69.343233</t>
-  </si>
-  <si>
     <t>41.364346</t>
   </si>
   <si>
@@ -1481,6 +1472,24 @@
   </si>
   <si>
     <t>1-сонли Шахар тугрихонаси рупараси</t>
+  </si>
+  <si>
+    <t>41.221559</t>
+  </si>
+  <si>
+    <t>69.208823</t>
+  </si>
+  <si>
+    <t>41.287658</t>
+  </si>
+  <si>
+    <t>69.283170</t>
+  </si>
+  <si>
+    <t>69.254583</t>
+  </si>
+  <si>
+    <t>41.250922</t>
   </si>
 </sst>
 </file>
@@ -2221,8 +2230,8 @@
       <c r="N9" t="s">
         <v>54</v>
       </c>
-      <c r="O9">
-        <v>41.280061000000003</v>
+      <c r="O9" t="s">
+        <v>486</v>
       </c>
       <c r="P9">
         <v>69.285818000000006</v>
@@ -2266,10 +2275,10 @@
         <v>58</v>
       </c>
       <c r="O10" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P10" t="s">
-        <v>449</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -2398,10 +2407,10 @@
         <v>70</v>
       </c>
       <c r="O13" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="P13" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -2485,11 +2494,11 @@
       <c r="N15" t="s">
         <v>79</v>
       </c>
-      <c r="O15">
-        <v>41.252921999999998</v>
-      </c>
-      <c r="P15">
-        <v>69.256793999999999</v>
+      <c r="O15" t="s">
+        <v>489</v>
+      </c>
+      <c r="P15" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -2559,7 +2568,7 @@
         <v>84</v>
       </c>
       <c r="J17" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="K17" t="s">
         <v>85</v>
@@ -2574,10 +2583,10 @@
         <v>86</v>
       </c>
       <c r="O17" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="P17" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -2662,10 +2671,10 @@
         <v>93</v>
       </c>
       <c r="O19" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="P19" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -2794,10 +2803,10 @@
         <v>106</v>
       </c>
       <c r="O22" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="P22" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -2838,10 +2847,10 @@
         <v>111</v>
       </c>
       <c r="O23" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="P23" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -3102,10 +3111,10 @@
         <v>134</v>
       </c>
       <c r="O29" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="P29" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -3228,7 +3237,7 @@
         <v>146</v>
       </c>
       <c r="O32" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="P32">
         <v>69.212119999999999</v>
@@ -3275,7 +3284,7 @@
         <v>41.288673000000003</v>
       </c>
       <c r="P33" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -3492,10 +3501,10 @@
         <v>172</v>
       </c>
       <c r="O38" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="P38" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -3668,10 +3677,10 @@
         <v>188</v>
       </c>
       <c r="O42" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="P42" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -3756,10 +3765,10 @@
         <v>196</v>
       </c>
       <c r="O44" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="P44" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -3844,10 +3853,10 @@
         <v>204</v>
       </c>
       <c r="O46" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P46" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -3932,10 +3941,10 @@
         <v>212</v>
       </c>
       <c r="O48" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="P48" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -4196,10 +4205,10 @@
         <v>237</v>
       </c>
       <c r="O54" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="P54" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
@@ -4328,10 +4337,10 @@
         <v>250</v>
       </c>
       <c r="O57" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="P57" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
@@ -4372,10 +4381,10 @@
         <v>254</v>
       </c>
       <c r="O58" t="s">
-        <v>446</v>
+        <v>484</v>
       </c>
       <c r="P58" t="s">
-        <v>447</v>
+        <v>485</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
@@ -4460,10 +4469,10 @@
         <v>262</v>
       </c>
       <c r="O60" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="P60" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
@@ -4812,10 +4821,10 @@
         <v>295</v>
       </c>
       <c r="O68" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="P68" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
@@ -5516,10 +5525,10 @@
         <v>360</v>
       </c>
       <c r="O84" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="P84" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
@@ -5736,10 +5745,10 @@
         <v>380</v>
       </c>
       <c r="O89" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P89" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">

--- a/dorixonalar.xlsx
+++ b/dorixonalar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\gpp\dorixona-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6E8430-B35C-4302-B419-197A20C09D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD40C6F9-55E3-4317-ACD4-D44C5925DC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="491">
   <si>
     <t>Filial №</t>
   </si>
@@ -1360,9 +1360,6 @@
     <t>асосий</t>
   </si>
   <si>
-    <t>41.255195</t>
-  </si>
-  <si>
     <t>41.364346</t>
   </si>
   <si>
@@ -1490,6 +1487,12 @@
   </si>
   <si>
     <t>41.250922</t>
+  </si>
+  <si>
+    <t>69.343336</t>
+  </si>
+  <si>
+    <t>41.255054</t>
   </si>
 </sst>
 </file>
@@ -2231,10 +2234,10 @@
         <v>54</v>
       </c>
       <c r="O9" t="s">
+        <v>485</v>
+      </c>
+      <c r="P9" t="s">
         <v>486</v>
-      </c>
-      <c r="P9">
-        <v>69.285818000000006</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -2275,10 +2278,10 @@
         <v>58</v>
       </c>
       <c r="O10" t="s">
-        <v>446</v>
+        <v>490</v>
       </c>
       <c r="P10" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -2407,10 +2410,10 @@
         <v>70</v>
       </c>
       <c r="O13" t="s">
+        <v>476</v>
+      </c>
+      <c r="P13" t="s">
         <v>477</v>
-      </c>
-      <c r="P13" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -2495,10 +2498,10 @@
         <v>79</v>
       </c>
       <c r="O15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="P15" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -2568,7 +2571,7 @@
         <v>84</v>
       </c>
       <c r="J17" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K17" t="s">
         <v>85</v>
@@ -2583,10 +2586,10 @@
         <v>86</v>
       </c>
       <c r="O17" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="P17" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -2671,10 +2674,10 @@
         <v>93</v>
       </c>
       <c r="O19" t="s">
+        <v>472</v>
+      </c>
+      <c r="P19" t="s">
         <v>473</v>
-      </c>
-      <c r="P19" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -2803,10 +2806,10 @@
         <v>106</v>
       </c>
       <c r="O22" t="s">
+        <v>450</v>
+      </c>
+      <c r="P22" t="s">
         <v>451</v>
-      </c>
-      <c r="P22" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -2847,10 +2850,10 @@
         <v>111</v>
       </c>
       <c r="O23" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="P23" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -3111,10 +3114,10 @@
         <v>134</v>
       </c>
       <c r="O29" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="P29" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -3237,7 +3240,7 @@
         <v>146</v>
       </c>
       <c r="O32" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="P32">
         <v>69.212119999999999</v>
@@ -3284,7 +3287,7 @@
         <v>41.288673000000003</v>
       </c>
       <c r="P33" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -3501,10 +3504,10 @@
         <v>172</v>
       </c>
       <c r="O38" t="s">
+        <v>448</v>
+      </c>
+      <c r="P38" t="s">
         <v>449</v>
-      </c>
-      <c r="P38" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -3677,10 +3680,10 @@
         <v>188</v>
       </c>
       <c r="O42" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="P42" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -3765,10 +3768,10 @@
         <v>196</v>
       </c>
       <c r="O44" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="P44" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -3853,10 +3856,10 @@
         <v>204</v>
       </c>
       <c r="O46" t="s">
+        <v>452</v>
+      </c>
+      <c r="P46" t="s">
         <v>453</v>
-      </c>
-      <c r="P46" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -3941,10 +3944,10 @@
         <v>212</v>
       </c>
       <c r="O48" t="s">
+        <v>464</v>
+      </c>
+      <c r="P48" t="s">
         <v>465</v>
-      </c>
-      <c r="P48" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -4205,10 +4208,10 @@
         <v>237</v>
       </c>
       <c r="O54" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
@@ -4337,10 +4340,10 @@
         <v>250</v>
       </c>
       <c r="O57" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P57" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
@@ -4381,10 +4384,10 @@
         <v>254</v>
       </c>
       <c r="O58" t="s">
+        <v>483</v>
+      </c>
+      <c r="P58" t="s">
         <v>484</v>
-      </c>
-      <c r="P58" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
@@ -4469,10 +4472,10 @@
         <v>262</v>
       </c>
       <c r="O60" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="P60" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
@@ -4821,10 +4824,10 @@
         <v>295</v>
       </c>
       <c r="O68" t="s">
+        <v>478</v>
+      </c>
+      <c r="P68" t="s">
         <v>479</v>
-      </c>
-      <c r="P68" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
@@ -5525,10 +5528,10 @@
         <v>360</v>
       </c>
       <c r="O84" t="s">
+        <v>470</v>
+      </c>
+      <c r="P84" t="s">
         <v>471</v>
-      </c>
-      <c r="P84" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
@@ -5745,10 +5748,10 @@
         <v>380</v>
       </c>
       <c r="O89" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="P89" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">

--- a/dorixonalar.xlsx
+++ b/dorixonalar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\gpp\dorixona-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD40C6F9-55E3-4317-ACD4-D44C5925DC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8354F957-ACE4-4566-B1F8-403E28ACD442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="493">
   <si>
     <t>Filial №</t>
   </si>
@@ -1462,27 +1462,12 @@
     <t xml:space="preserve">69.216266 </t>
   </si>
   <si>
-    <t>69.218276</t>
-  </si>
-  <si>
-    <t>41.322175</t>
-  </si>
-  <si>
-    <t>1-сонли Шахар тугрихонаси рупараси</t>
-  </si>
-  <si>
     <t>41.221559</t>
   </si>
   <si>
     <t>69.208823</t>
   </si>
   <si>
-    <t>41.287658</t>
-  </si>
-  <si>
-    <t>69.283170</t>
-  </si>
-  <si>
     <t>69.254583</t>
   </si>
   <si>
@@ -1493,6 +1478,27 @@
   </si>
   <si>
     <t>41.255054</t>
+  </si>
+  <si>
+    <t>67.089765</t>
+  </si>
+  <si>
+    <t>39.602783</t>
+  </si>
+  <si>
+    <t>69.218275</t>
+  </si>
+  <si>
+    <t>41.322369</t>
+  </si>
+  <si>
+    <t>69.283426</t>
+  </si>
+  <si>
+    <t>41.28751</t>
+  </si>
+  <si>
+    <t>1-сон шахар клиник шифохонаси, тугрукхона рупараси</t>
   </si>
 </sst>
 </file>
@@ -2234,10 +2240,10 @@
         <v>54</v>
       </c>
       <c r="O9" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="P9" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -2278,10 +2284,10 @@
         <v>58</v>
       </c>
       <c r="O10" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="P10" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -2498,10 +2504,10 @@
         <v>79</v>
       </c>
       <c r="O15" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="P15" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -2571,10 +2577,10 @@
         <v>84</v>
       </c>
       <c r="J17" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="K17" t="s">
-        <v>85</v>
+        <v>492</v>
       </c>
       <c r="L17" t="s">
         <v>20</v>
@@ -2586,10 +2592,10 @@
         <v>86</v>
       </c>
       <c r="O17" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="P17" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -3591,11 +3597,11 @@
       <c r="N40" t="s">
         <v>180</v>
       </c>
-      <c r="O40">
-        <v>39.595314000000002</v>
-      </c>
-      <c r="P40">
-        <v>67.089285000000004</v>
+      <c r="O40" t="s">
+        <v>487</v>
+      </c>
+      <c r="P40" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -4384,10 +4390,10 @@
         <v>254</v>
       </c>
       <c r="O58" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="P58" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">

--- a/dorixonalar.xlsx
+++ b/dorixonalar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\gpp\dorixona-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8354F957-ACE4-4566-B1F8-403E28ACD442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADDC089-6E55-4239-8310-ED8B666D8B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="499">
   <si>
     <t>Filial №</t>
   </si>
@@ -1499,6 +1499,24 @@
   </si>
   <si>
     <t>1-сон шахар клиник шифохонаси, тугрукхона рупараси</t>
+  </si>
+  <si>
+    <t>41.204489</t>
+  </si>
+  <si>
+    <t>69.227648</t>
+  </si>
+  <si>
+    <t>69.345592</t>
+  </si>
+  <si>
+    <t>41.285519</t>
+  </si>
+  <si>
+    <t>41.295130</t>
+  </si>
+  <si>
+    <t>69.334867</t>
   </si>
 </sst>
 </file>
@@ -2635,11 +2653,11 @@
       <c r="N18" t="s">
         <v>90</v>
       </c>
-      <c r="O18">
-        <v>41.303612000000001</v>
-      </c>
-      <c r="P18">
-        <v>69.303685999999999</v>
+      <c r="O18" t="s">
+        <v>497</v>
+      </c>
+      <c r="P18" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -4785,11 +4803,11 @@
       <c r="N67" t="s">
         <v>291</v>
       </c>
-      <c r="O67">
-        <v>41.285631000000002</v>
-      </c>
-      <c r="P67">
-        <v>69.346453999999994</v>
+      <c r="O67" t="s">
+        <v>496</v>
+      </c>
+      <c r="P67" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
@@ -6061,11 +6079,11 @@
       <c r="N96" t="s">
         <v>409</v>
       </c>
-      <c r="O96">
-        <v>41.20431</v>
-      </c>
-      <c r="P96">
-        <v>69.228810999999993</v>
+      <c r="O96" t="s">
+        <v>493</v>
+      </c>
+      <c r="P96" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
